--- a/cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-24 17:39</t>
+          <t>Generated: 2026-08-29 11:02</t>
         </is>
       </c>
     </row>
@@ -573,95 +573,168 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>System: explicit LOINC-system -&gt; COSMoS-term sets (see notebook section 3); systems outside the map report UNMAPPED, never guessed.</t>
+          <t>PACKAGE_UNBOUND: LOINC Ord/Nom vs derived Text where the DSS binds no value set on --ORRES - no package claim to disagree with; the gap is the missing value set.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OPEN derived system: LOINC system checked against the specimen value list the DSS offers -&gt; OPEN_COMPATIBLE means LOINC names the pin the package implies.</t>
+          <t>System: explicit LOINC-system -&gt; COSMoS-term sets (see notebook section 3); systems outside the map report UNMAPPED, never guessed.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>OPEN derived system: LOINC system checked against the specimen value list the DSS offers -&gt; OPEN_COMPATIBLE means LOINC names the pin the package implies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Method: BOTH_PINNED / LOINC_ONLY (LOINC says method matters, DSS does not pin) / COSMOS_ONLY / NEITHER.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DSS x pinned-LOINC pairs compared: 183</t>
+          <t>SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>System verdicts: AGREE: 177, NOT_COMPARABLE: 3, DISAGREE: 3</t>
+          <t>DSS x pinned-LOINC pairs compared: 183</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Scale verdicts: AGREE: 152, DISAGREE: 31</t>
+          <t>Coverage: 140 of 1247 in-scope DSS carry a LOINC pin - agreement validates the derivation rules on the pinned subset, not the corpus.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Method verdicts: LOINC_ONLY: 177, BOTH_PINNED: 6</t>
+          <t>System verdicts: AGREE: 177, NOT_COMPARABLE: 3, DISAGREE: 3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Rows with a system or scale problem: 34</t>
+          <t>Scale verdicts: AGREE: 152, PACKAGE_UNBOUND: 30, DISAGREE: 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Multi-code DSS: 42, of which property-axis-only (unit-dimension recording variants): 39</t>
+          <t>Method verdicts: NEITHER: 159, LOINC_ONLY: 18, BOTH_PINNED: 6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Glucose family: 99 LOINC codes; system gap: 41, time-aspect variant (no COSMoS axis): 20, recording variant of covered observable: 13, generic documentation code: 11, pinned in COSMoS: 10, non-clinical / other: 4</t>
+          <t>Rows with a system or scale finding: 34 (PACKAGE_UNBOUND 30; real scale disagreements 1; system disagreements 3)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Multi-code DSS: 42, of which property-axis-only (unit-dimension recording variants): 39</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>Glucose family: 99 LOINC codes; system gap: 41, time-aspect variant (no COSMoS axis): 20, recording variant of covered observable: 13, generic documentation code: 11, pinned in COSMoS: 10, non-clinical / other: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FINDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Suspected COSMoS pin errors (system DISAGREE, graph-verified):</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HGBBLDDIP: pins 49137-3 (Hemoglobin; LOINC system Urine) on derived system BLOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NICOTINEURIN: pins 55557-3 (Nicotine; LOINC system Ser/Plas) on derived system URINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NICOTINEURIN: pins 3853-9 (Nicotine; LOINC system Ser/Plas) on derived system URINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate pin across BCs (one LOINC observable, two COSMoS BCs - the reverse of the glucose case): 33051-4 on OCCBLDURINPRES;RBCURINPRES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Scale: 30 of 31 non-agreeing scale rows are PACKAGE_UNBOUND - the missing-value-set finding holds corpus-wide; real disagreements: HCGSERPL (Ord vs Quantitative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Glucose family: 20 timed-collection variants in LOINC with no COSMoS collection-duration axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>COLOR CONVENTION</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Yellow FFD700 = COSMoS package identifiers. Blue 2E5C8A = LOINC service content (external source). Grey 7F7F7F = derived values and verdicts.</t>
         </is>
@@ -678,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T184"/>
+  <dimension ref="A1:U184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -697,10 +770,11 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,20 +860,25 @@
       </c>
       <c r="Q1" s="5" t="inlineStr">
         <is>
+          <t>orres_value_binding</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
           <t>spec_value_list</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>system_verdict</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>scale_verdict</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>method_verdict</t>
         </is>
@@ -886,18 +965,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="n"/>
-      <c r="R2" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="n"/>
       <c r="S2" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -984,18 +1068,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="n"/>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="n"/>
       <c r="S3" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -1078,12 +1167,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="n"/>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="n"/>
       <c r="S4" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -1091,7 +1180,12 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1266,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="n"/>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="n"/>
       <c r="S5" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -1185,7 +1279,12 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1365,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="n"/>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="n"/>
       <c r="S6" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -1279,7 +1378,12 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1356,20 +1460,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="n"/>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1559,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="n"/>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -1463,7 +1572,12 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1658,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="n"/>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="n"/>
       <c r="S9" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -1557,7 +1671,12 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1634,20 +1753,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="n"/>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1724,20 +1848,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="n"/>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="n"/>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -1822,18 +1951,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="n"/>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -1920,18 +2054,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="n"/>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -2014,12 +2153,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="n"/>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="n"/>
       <c r="S14" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2027,7 +2166,12 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2252,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="n"/>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2121,7 +2265,12 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2351,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q16" s="8" t="n"/>
-      <c r="R16" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="n"/>
       <c r="S16" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2215,7 +2364,12 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2450,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="n"/>
       <c r="S17" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2309,7 +2463,12 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2549,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2403,7 +2562,12 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2648,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="n"/>
       <c r="S19" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2497,7 +2661,12 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2747,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2591,7 +2760,12 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2846,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2685,7 +2859,12 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2945,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2779,7 +2958,12 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2856,20 +3040,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -2950,12 +3139,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="n"/>
       <c r="S24" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -2963,7 +3152,12 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3238,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="n"/>
       <c r="S25" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3057,7 +3251,12 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3337,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="n"/>
       <c r="S26" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3151,7 +3350,12 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3436,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="n"/>
       <c r="S27" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3245,7 +3449,12 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3535,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3339,7 +3548,12 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3420,12 +3634,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="n"/>
       <c r="S29" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3433,7 +3647,12 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3514,12 +3733,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q30" s="8" t="n"/>
-      <c r="R30" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3527,7 +3746,12 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3832,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q31" s="8" t="n"/>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="n"/>
       <c r="S31" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3621,7 +3845,12 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3931,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q32" s="8" t="n"/>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3715,7 +3944,12 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3796,12 +4030,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q33" s="8" t="n"/>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="n"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3809,7 +4043,12 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3890,12 +4129,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3903,7 +4142,12 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -3984,12 +4228,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q35" s="8" t="n"/>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="n"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -3997,7 +4241,12 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4327,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q36" s="8" t="n"/>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4091,7 +4340,12 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4172,20 +4426,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q37" s="8" t="n"/>
-      <c r="R37" s="8" t="inlineStr">
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="n"/>
+      <c r="S37" s="8" t="inlineStr">
         <is>
           <t>NOT_COMPARABLE</t>
         </is>
       </c>
-      <c r="S37" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4525,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q38" s="8" t="n"/>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4279,7 +4538,12 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4624,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q39" s="8" t="n"/>
-      <c r="R39" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="n"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4373,7 +4637,12 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4450,20 +4719,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q40" s="8" t="n"/>
-      <c r="R40" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4818,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q41" s="8" t="n"/>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="n"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4557,7 +4831,12 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4638,12 +4917,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q42" s="8" t="n"/>
-      <c r="R42" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4651,7 +4930,12 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4732,12 +5016,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q43" s="8" t="n"/>
-      <c r="R43" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="n"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4745,7 +5029,12 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4826,12 +5115,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q44" s="8" t="n"/>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4839,7 +5128,12 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -4920,12 +5214,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q45" s="8" t="n"/>
-      <c r="R45" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R45" s="8" t="n"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -4933,7 +5227,12 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5313,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q46" s="8" t="n"/>
-      <c r="R46" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5027,7 +5326,12 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5108,12 +5412,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q47" s="8" t="n"/>
-      <c r="R47" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="n"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5121,7 +5425,12 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5202,12 +5511,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q48" s="8" t="n"/>
-      <c r="R48" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5215,7 +5524,12 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5610,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q49" s="8" t="n"/>
-      <c r="R49" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q49" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R49" s="8" t="n"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5309,7 +5623,12 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5709,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q50" s="8" t="n"/>
-      <c r="R50" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q50" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5403,7 +5722,12 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5488,18 +5812,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q51" s="8" t="n"/>
-      <c r="R51" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q51" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R51" s="8" t="n"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -5586,18 +5915,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q52" s="8" t="n"/>
-      <c r="R52" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q52" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R52" s="8" t="n"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -5680,12 +6014,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q53" s="8" t="n"/>
-      <c r="R53" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="n"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5693,7 +6027,12 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5774,12 +6113,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q54" s="8" t="n"/>
-      <c r="R54" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5787,7 +6126,12 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5868,12 +6212,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q55" s="8" t="n"/>
-      <c r="R55" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R55" s="8" t="n"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5881,7 +6225,12 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -5962,12 +6311,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q56" s="8" t="n"/>
-      <c r="R56" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q56" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R56" s="8" t="n"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -5975,7 +6324,12 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6056,12 +6410,12 @@
           <t>UNBOUND</t>
         </is>
       </c>
-      <c r="Q57" s="8" t="n"/>
-      <c r="R57" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q57" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R57" s="8" t="n"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6069,7 +6423,12 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6509,12 @@
           <t>UNBOUND</t>
         </is>
       </c>
-      <c r="Q58" s="8" t="n"/>
-      <c r="R58" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R58" s="8" t="n"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6163,7 +6522,12 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6244,12 +6608,12 @@
           <t>UNBOUND</t>
         </is>
       </c>
-      <c r="Q59" s="8" t="n"/>
-      <c r="R59" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R59" s="8" t="n"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6257,7 +6621,12 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6338,12 +6707,12 @@
           <t>UNBOUND</t>
         </is>
       </c>
-      <c r="Q60" s="8" t="n"/>
-      <c r="R60" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q60" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R60" s="8" t="n"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6351,7 +6720,12 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6432,12 +6806,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q61" s="8" t="n"/>
-      <c r="R61" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q61" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R61" s="8" t="n"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6445,7 +6819,12 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6905,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q62" s="8" t="n"/>
-      <c r="R62" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R62" s="8" t="n"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6539,7 +6918,12 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6620,18 +7004,23 @@
           <t>TEST STRIP</t>
         </is>
       </c>
-      <c r="Q63" s="8" t="n"/>
-      <c r="R63" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R63" s="8" t="n"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -6714,12 +7103,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q64" s="8" t="n"/>
-      <c r="R64" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q64" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R64" s="8" t="n"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6727,7 +7116,12 @@
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6808,12 +7202,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q65" s="8" t="n"/>
-      <c r="R65" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R65" s="8" t="n"/>
       <c r="S65" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -6821,7 +7215,12 @@
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6898,20 +7297,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q66" s="8" t="n"/>
-      <c r="R66" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q66" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R66" s="8" t="n"/>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U66" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -6992,12 +7396,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q67" s="8" t="n"/>
-      <c r="R67" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R67" s="8" t="n"/>
       <c r="S67" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7005,7 +7409,12 @@
       </c>
       <c r="T67" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7495,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q68" s="8" t="n"/>
-      <c r="R68" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q68" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R68" s="8" t="n"/>
       <c r="S68" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7099,7 +7508,12 @@
       </c>
       <c r="T68" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U68" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7180,12 +7594,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q69" s="8" t="n"/>
-      <c r="R69" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R69" s="8" t="n"/>
       <c r="S69" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7193,7 +7607,12 @@
       </c>
       <c r="T69" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U69" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7693,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q70" s="8" t="n"/>
-      <c r="R70" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q70" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R70" s="8" t="n"/>
       <c r="S70" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7287,7 +7706,12 @@
       </c>
       <c r="T70" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7364,20 +7788,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q71" s="8" t="n"/>
-      <c r="R71" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R71" s="8" t="n"/>
       <c r="S71" s="8" t="inlineStr">
         <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>LOINC_ONLY</t>
+      <c r="U71" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7454,20 +7883,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q72" s="8" t="n"/>
-      <c r="R72" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q72" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R72" s="8" t="n"/>
       <c r="S72" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T72" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7552,18 +7986,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q73" s="8" t="n"/>
-      <c r="R73" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R73" s="8" t="n"/>
       <c r="S73" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U73" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -7646,12 +8085,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q74" s="8" t="n"/>
-      <c r="R74" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q74" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R74" s="8" t="n"/>
       <c r="S74" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7659,7 +8098,12 @@
       </c>
       <c r="T74" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U74" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7740,12 +8184,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q75" s="8" t="n"/>
-      <c r="R75" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R75" s="8" t="n"/>
       <c r="S75" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7753,7 +8197,12 @@
       </c>
       <c r="T75" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U75" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7834,12 +8283,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q76" s="8" t="n"/>
-      <c r="R76" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q76" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R76" s="8" t="n"/>
       <c r="S76" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7847,7 +8296,12 @@
       </c>
       <c r="T76" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -7928,12 +8382,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q77" s="8" t="n"/>
-      <c r="R77" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R77" s="8" t="n"/>
       <c r="S77" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -7941,7 +8395,12 @@
       </c>
       <c r="T77" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U77" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8026,18 +8485,23 @@
           <t>DIPSTICK MEASUREMENT METHOD</t>
         </is>
       </c>
-      <c r="Q78" s="8" t="n"/>
-      <c r="R78" s="8" t="inlineStr">
+      <c r="Q78" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R78" s="8" t="n"/>
+      <c r="S78" s="8" t="inlineStr">
         <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="S78" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U78" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -8124,18 +8588,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q79" s="8" t="n"/>
-      <c r="R79" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R79" s="8" t="n"/>
       <c r="S79" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U79" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -8222,18 +8691,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q80" s="8" t="n"/>
-      <c r="R80" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R80" s="8" t="n"/>
       <c r="S80" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U80" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -8316,12 +8790,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q81" s="8" t="n"/>
-      <c r="R81" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R81" s="8" t="n"/>
       <c r="S81" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8329,7 +8803,12 @@
       </c>
       <c r="T81" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U81" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8889,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q82" s="8" t="n"/>
-      <c r="R82" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R82" s="8" t="n"/>
       <c r="S82" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8423,7 +8902,12 @@
       </c>
       <c r="T82" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U82" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8988,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q83" s="8" t="n"/>
-      <c r="R83" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R83" s="8" t="n"/>
       <c r="S83" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8517,7 +9001,12 @@
       </c>
       <c r="T83" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U83" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8598,12 +9087,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q84" s="8" t="n"/>
-      <c r="R84" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q84" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R84" s="8" t="n"/>
       <c r="S84" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8611,7 +9100,12 @@
       </c>
       <c r="T84" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U84" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8692,12 +9186,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q85" s="8" t="n"/>
-      <c r="R85" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R85" s="8" t="n"/>
       <c r="S85" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8705,7 +9199,12 @@
       </c>
       <c r="T85" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8782,20 +9281,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q86" s="8" t="n"/>
-      <c r="R86" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q86" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R86" s="8" t="n"/>
       <c r="S86" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T86" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U86" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8876,12 +9380,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q87" s="8" t="n"/>
-      <c r="R87" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R87" s="8" t="n"/>
       <c r="S87" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8889,7 +9393,12 @@
       </c>
       <c r="T87" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -8970,12 +9479,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q88" s="8" t="n"/>
-      <c r="R88" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R88" s="8" t="n"/>
       <c r="S88" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -8983,7 +9492,12 @@
       </c>
       <c r="T88" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9068,18 +9582,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q89" s="8" t="n"/>
-      <c r="R89" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R89" s="8" t="n"/>
       <c r="S89" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -9162,12 +9681,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q90" s="8" t="n"/>
-      <c r="R90" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R90" s="8" t="n"/>
       <c r="S90" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -9175,7 +9694,12 @@
       </c>
       <c r="T90" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U90" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9256,12 +9780,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q91" s="8" t="n"/>
-      <c r="R91" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R91" s="8" t="n"/>
       <c r="S91" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -9269,7 +9793,12 @@
       </c>
       <c r="T91" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9350,12 +9879,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q92" s="8" t="n"/>
-      <c r="R92" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R92" s="8" t="n"/>
       <c r="S92" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -9363,7 +9892,12 @@
       </c>
       <c r="T92" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U92" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9444,18 +9978,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q93" s="8" t="n"/>
-      <c r="R93" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R93" s="8" t="n"/>
       <c r="S93" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T93" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U93" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -9534,20 +10073,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q94" s="8" t="n"/>
-      <c r="R94" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R94" s="8" t="n"/>
       <c r="S94" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T94" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U94" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9628,18 +10172,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q95" s="8" t="n"/>
-      <c r="R95" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R95" s="8" t="n"/>
       <c r="S95" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T95" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U95" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -9722,12 +10271,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q96" s="8" t="n"/>
-      <c r="R96" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q96" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R96" s="8" t="n"/>
       <c r="S96" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -9735,7 +10284,12 @@
       </c>
       <c r="T96" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U96" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9816,12 +10370,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q97" s="8" t="n"/>
-      <c r="R97" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q97" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R97" s="8" t="n"/>
       <c r="S97" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -9829,7 +10383,12 @@
       </c>
       <c r="T97" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U97" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -9910,12 +10469,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q98" s="8" t="n"/>
-      <c r="R98" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q98" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R98" s="8" t="n"/>
       <c r="S98" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -9923,7 +10482,12 @@
       </c>
       <c r="T98" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U98" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10004,12 +10568,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q99" s="8" t="n"/>
-      <c r="R99" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q99" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R99" s="8" t="n"/>
       <c r="S99" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10017,7 +10581,12 @@
       </c>
       <c r="T99" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U99" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10098,12 +10667,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q100" s="8" t="n"/>
-      <c r="R100" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q100" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R100" s="8" t="n"/>
       <c r="S100" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10111,7 +10680,12 @@
       </c>
       <c r="T100" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U100" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10192,12 +10766,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q101" s="8" t="n"/>
-      <c r="R101" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q101" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R101" s="8" t="n"/>
       <c r="S101" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10205,7 +10779,12 @@
       </c>
       <c r="T101" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U101" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10282,20 +10861,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q102" s="8" t="n"/>
-      <c r="R102" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q102" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R102" s="8" t="n"/>
       <c r="S102" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T102" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U102" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10376,12 +10960,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q103" s="8" t="n"/>
-      <c r="R103" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q103" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R103" s="8" t="n"/>
       <c r="S103" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10389,7 +10973,12 @@
       </c>
       <c r="T103" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U103" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10470,18 +11059,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q104" s="8" t="n"/>
-      <c r="R104" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q104" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R104" s="8" t="n"/>
       <c r="S104" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T104" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U104" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -10564,18 +11158,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q105" s="8" t="n"/>
-      <c r="R105" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R105" s="8" t="n"/>
       <c r="S105" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T105" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U105" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -10658,12 +11257,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q106" s="8" t="n"/>
-      <c r="R106" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q106" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R106" s="8" t="n"/>
       <c r="S106" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10671,7 +11270,12 @@
       </c>
       <c r="T106" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U106" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10752,12 +11356,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q107" s="8" t="n"/>
-      <c r="R107" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q107" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R107" s="8" t="n"/>
       <c r="S107" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10765,7 +11369,12 @@
       </c>
       <c r="T107" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U107" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10846,12 +11455,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q108" s="8" t="n"/>
-      <c r="R108" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q108" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R108" s="8" t="n"/>
       <c r="S108" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10859,7 +11468,12 @@
       </c>
       <c r="T108" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U108" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -10940,12 +11554,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q109" s="8" t="n"/>
-      <c r="R109" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q109" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R109" s="8" t="n"/>
       <c r="S109" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -10953,7 +11567,12 @@
       </c>
       <c r="T109" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U109" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11034,12 +11653,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q110" s="8" t="n"/>
-      <c r="R110" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q110" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R110" s="8" t="n"/>
       <c r="S110" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11047,7 +11666,12 @@
       </c>
       <c r="T110" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U110" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11128,12 +11752,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q111" s="8" t="n"/>
-      <c r="R111" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q111" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R111" s="8" t="n"/>
       <c r="S111" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11141,7 +11765,12 @@
       </c>
       <c r="T111" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U111" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11222,12 +11851,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q112" s="8" t="n"/>
-      <c r="R112" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q112" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R112" s="8" t="n"/>
       <c r="S112" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11235,7 +11864,12 @@
       </c>
       <c r="T112" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U112" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11316,12 +11950,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q113" s="8" t="n"/>
-      <c r="R113" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q113" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R113" s="8" t="n"/>
       <c r="S113" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11329,7 +11963,12 @@
       </c>
       <c r="T113" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U113" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11410,12 +12049,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q114" s="8" t="n"/>
-      <c r="R114" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q114" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R114" s="8" t="n"/>
       <c r="S114" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11423,7 +12062,12 @@
       </c>
       <c r="T114" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U114" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11504,20 +12148,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q115" s="8" t="n"/>
-      <c r="R115" s="8" t="inlineStr">
+      <c r="Q115" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R115" s="8" t="n"/>
+      <c r="S115" s="8" t="inlineStr">
         <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="S115" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T115" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U115" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11598,20 +12247,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q116" s="8" t="n"/>
-      <c r="R116" s="8" t="inlineStr">
+      <c r="Q116" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R116" s="8" t="n"/>
+      <c r="S116" s="8" t="inlineStr">
         <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="S116" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T116" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U116" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11692,12 +12346,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q117" s="8" t="n"/>
-      <c r="R117" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q117" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R117" s="8" t="n"/>
       <c r="S117" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11705,7 +12359,12 @@
       </c>
       <c r="T117" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U117" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11782,20 +12441,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q118" s="8" t="n"/>
-      <c r="R118" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q118" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R118" s="8" t="n"/>
       <c r="S118" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T118" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U118" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11876,12 +12540,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q119" s="8" t="n"/>
-      <c r="R119" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q119" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R119" s="8" t="n"/>
       <c r="S119" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -11889,7 +12553,12 @@
       </c>
       <c r="T119" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U119" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -11966,20 +12635,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q120" s="8" t="n"/>
-      <c r="R120" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q120" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R120" s="8" t="n"/>
       <c r="S120" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T120" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U120" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12056,20 +12730,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q121" s="8" t="n"/>
-      <c r="R121" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q121" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R121" s="8" t="n"/>
       <c r="S121" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T121" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U121" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12146,20 +12825,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q122" s="8" t="n"/>
-      <c r="R122" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q122" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R122" s="8" t="n"/>
       <c r="S122" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T122" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U122" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12924,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q123" s="8" t="n"/>
-      <c r="R123" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q123" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R123" s="8" t="n"/>
       <c r="S123" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -12253,7 +12937,12 @@
       </c>
       <c r="T123" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U123" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12334,12 +13023,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q124" s="8" t="n"/>
-      <c r="R124" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q124" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R124" s="8" t="n"/>
       <c r="S124" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -12347,7 +13036,12 @@
       </c>
       <c r="T124" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U124" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12428,12 +13122,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q125" s="8" t="n"/>
-      <c r="R125" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q125" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R125" s="8" t="n"/>
       <c r="S125" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -12441,7 +13135,12 @@
       </c>
       <c r="T125" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U125" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12522,12 +13221,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q126" s="8" t="n"/>
-      <c r="R126" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q126" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R126" s="8" t="n"/>
       <c r="S126" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -12535,7 +13234,12 @@
       </c>
       <c r="T126" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U126" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12616,12 +13320,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q127" s="8" t="n"/>
-      <c r="R127" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q127" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R127" s="8" t="n"/>
       <c r="S127" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -12629,7 +13333,12 @@
       </c>
       <c r="T127" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U127" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12710,20 +13419,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q128" s="8" t="n"/>
-      <c r="R128" s="8" t="inlineStr">
+      <c r="Q128" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R128" s="8" t="n"/>
+      <c r="S128" s="8" t="inlineStr">
         <is>
           <t>NOT_COMPARABLE</t>
         </is>
       </c>
-      <c r="S128" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T128" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U128" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12800,20 +13514,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q129" s="8" t="n"/>
-      <c r="R129" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q129" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R129" s="8" t="n"/>
       <c r="S129" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T129" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U129" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12890,20 +13609,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q130" s="8" t="n"/>
-      <c r="R130" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q130" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R130" s="8" t="n"/>
       <c r="S130" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T130" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U130" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -12984,12 +13708,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q131" s="8" t="n"/>
-      <c r="R131" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q131" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R131" s="8" t="n"/>
       <c r="S131" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -12997,7 +13721,12 @@
       </c>
       <c r="T131" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U131" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13078,12 +13807,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q132" s="8" t="n"/>
-      <c r="R132" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q132" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R132" s="8" t="n"/>
       <c r="S132" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -13091,7 +13820,12 @@
       </c>
       <c r="T132" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U132" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13172,12 +13906,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q133" s="8" t="n"/>
-      <c r="R133" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q133" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R133" s="8" t="n"/>
       <c r="S133" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -13185,7 +13919,12 @@
       </c>
       <c r="T133" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U133" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13266,12 +14005,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q134" s="8" t="n"/>
-      <c r="R134" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q134" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R134" s="8" t="n"/>
       <c r="S134" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -13279,7 +14018,12 @@
       </c>
       <c r="T134" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U134" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13360,12 +14104,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q135" s="8" t="n"/>
-      <c r="R135" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q135" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R135" s="8" t="n"/>
       <c r="S135" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -13373,7 +14117,12 @@
       </c>
       <c r="T135" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U135" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13450,20 +14199,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q136" s="8" t="n"/>
-      <c r="R136" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q136" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R136" s="8" t="n"/>
       <c r="S136" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T136" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U136" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13548,18 +14302,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q137" s="8" t="n"/>
-      <c r="R137" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q137" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R137" s="8" t="n"/>
       <c r="S137" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T137" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U137" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -13646,18 +14405,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q138" s="8" t="n"/>
-      <c r="R138" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q138" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R138" s="8" t="n"/>
       <c r="S138" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T138" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U138" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -13744,18 +14508,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q139" s="8" t="n"/>
-      <c r="R139" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q139" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R139" s="8" t="n"/>
       <c r="S139" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T139" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U139" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -13838,12 +14607,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q140" s="8" t="n"/>
-      <c r="R140" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q140" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R140" s="8" t="n"/>
       <c r="S140" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -13851,7 +14620,12 @@
       </c>
       <c r="T140" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U140" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -13932,12 +14706,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q141" s="8" t="n"/>
-      <c r="R141" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q141" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R141" s="8" t="n"/>
       <c r="S141" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -13945,7 +14719,12 @@
       </c>
       <c r="T141" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U141" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14030,18 +14809,23 @@
           <t>DIPSTICK MEASUREMENT METHOD</t>
         </is>
       </c>
-      <c r="Q142" s="8" t="n"/>
-      <c r="R142" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q142" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R142" s="8" t="n"/>
       <c r="S142" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T142" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U142" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -14120,20 +14904,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q143" s="8" t="n"/>
-      <c r="R143" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q143" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R143" s="8" t="n"/>
       <c r="S143" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T143" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U143" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14210,20 +14999,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q144" s="8" t="n"/>
-      <c r="R144" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q144" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R144" s="8" t="n"/>
       <c r="S144" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T144" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U144" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14304,12 +15098,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q145" s="8" t="n"/>
-      <c r="R145" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q145" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R145" s="8" t="n"/>
       <c r="S145" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14317,7 +15111,12 @@
       </c>
       <c r="T145" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U145" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14398,12 +15197,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q146" s="8" t="n"/>
-      <c r="R146" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q146" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R146" s="8" t="n"/>
       <c r="S146" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14411,7 +15210,12 @@
       </c>
       <c r="T146" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U146" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14492,12 +15296,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q147" s="8" t="n"/>
-      <c r="R147" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q147" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R147" s="8" t="n"/>
       <c r="S147" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14505,7 +15309,12 @@
       </c>
       <c r="T147" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U147" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14582,12 +15391,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q148" s="8" t="n"/>
-      <c r="R148" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q148" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R148" s="8" t="n"/>
       <c r="S148" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14595,7 +15404,12 @@
       </c>
       <c r="T148" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U148" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14676,12 +15490,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q149" s="8" t="n"/>
-      <c r="R149" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q149" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R149" s="8" t="n"/>
       <c r="S149" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14689,7 +15503,12 @@
       </c>
       <c r="T149" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U149" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14770,12 +15589,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q150" s="8" t="n"/>
-      <c r="R150" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q150" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R150" s="8" t="n"/>
       <c r="S150" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14783,7 +15602,12 @@
       </c>
       <c r="T150" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U150" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14864,12 +15688,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q151" s="8" t="n"/>
-      <c r="R151" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q151" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R151" s="8" t="n"/>
       <c r="S151" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -14877,7 +15701,12 @@
       </c>
       <c r="T151" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U151" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -14962,18 +15791,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q152" s="8" t="n"/>
-      <c r="R152" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q152" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R152" s="8" t="n"/>
       <c r="S152" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T152" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U152" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -15056,12 +15890,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q153" s="8" t="n"/>
-      <c r="R153" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q153" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R153" s="8" t="n"/>
       <c r="S153" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15069,7 +15903,12 @@
       </c>
       <c r="T153" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U153" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15150,12 +15989,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q154" s="8" t="n"/>
-      <c r="R154" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q154" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R154" s="8" t="n"/>
       <c r="S154" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15163,7 +16002,12 @@
       </c>
       <c r="T154" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U154" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15244,12 +16088,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q155" s="8" t="n"/>
-      <c r="R155" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q155" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R155" s="8" t="n"/>
       <c r="S155" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15257,7 +16101,12 @@
       </c>
       <c r="T155" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U155" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15338,12 +16187,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q156" s="8" t="n"/>
-      <c r="R156" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q156" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R156" s="8" t="n"/>
       <c r="S156" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15351,7 +16200,12 @@
       </c>
       <c r="T156" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U156" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15432,12 +16286,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q157" s="8" t="n"/>
-      <c r="R157" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q157" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R157" s="8" t="n"/>
       <c r="S157" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15445,7 +16299,12 @@
       </c>
       <c r="T157" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U157" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15526,12 +16385,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q158" s="8" t="n"/>
-      <c r="R158" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q158" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R158" s="8" t="n"/>
       <c r="S158" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15539,7 +16398,12 @@
       </c>
       <c r="T158" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U158" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15620,12 +16484,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q159" s="8" t="n"/>
-      <c r="R159" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q159" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R159" s="8" t="n"/>
       <c r="S159" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15633,7 +16497,12 @@
       </c>
       <c r="T159" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U159" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15714,12 +16583,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q160" s="8" t="n"/>
-      <c r="R160" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q160" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R160" s="8" t="n"/>
       <c r="S160" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15727,7 +16596,12 @@
       </c>
       <c r="T160" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U160" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15808,12 +16682,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q161" s="8" t="n"/>
-      <c r="R161" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q161" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R161" s="8" t="n"/>
       <c r="S161" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15821,7 +16695,12 @@
       </c>
       <c r="T161" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U161" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15902,12 +16781,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q162" s="8" t="n"/>
-      <c r="R162" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q162" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R162" s="8" t="n"/>
       <c r="S162" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -15915,7 +16794,12 @@
       </c>
       <c r="T162" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U162" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -15996,12 +16880,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q163" s="8" t="n"/>
-      <c r="R163" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q163" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R163" s="8" t="n"/>
       <c r="S163" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16009,7 +16893,12 @@
       </c>
       <c r="T163" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U163" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16090,12 +16979,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q164" s="8" t="n"/>
-      <c r="R164" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q164" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R164" s="8" t="n"/>
       <c r="S164" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16103,7 +16992,12 @@
       </c>
       <c r="T164" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U164" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16184,12 +17078,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q165" s="8" t="n"/>
-      <c r="R165" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q165" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R165" s="8" t="n"/>
       <c r="S165" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16197,7 +17091,12 @@
       </c>
       <c r="T165" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U165" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16278,12 +17177,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q166" s="8" t="n"/>
-      <c r="R166" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q166" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R166" s="8" t="n"/>
       <c r="S166" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16291,7 +17190,12 @@
       </c>
       <c r="T166" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U166" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16368,20 +17272,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q167" s="8" t="n"/>
-      <c r="R167" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q167" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R167" s="8" t="n"/>
       <c r="S167" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T167" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U167" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16462,12 +17371,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q168" s="8" t="n"/>
-      <c r="R168" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q168" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R168" s="8" t="n"/>
       <c r="S168" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16475,7 +17384,12 @@
       </c>
       <c r="T168" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U168" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16556,12 +17470,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q169" s="8" t="n"/>
-      <c r="R169" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q169" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R169" s="8" t="n"/>
       <c r="S169" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16569,7 +17483,12 @@
       </c>
       <c r="T169" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U169" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16650,12 +17569,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q170" s="8" t="n"/>
-      <c r="R170" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q170" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R170" s="8" t="n"/>
       <c r="S170" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16663,7 +17582,12 @@
       </c>
       <c r="T170" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U170" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16744,12 +17668,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q171" s="8" t="n"/>
-      <c r="R171" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q171" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R171" s="8" t="n"/>
       <c r="S171" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16757,7 +17681,12 @@
       </c>
       <c r="T171" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U171" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16838,12 +17767,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q172" s="8" t="n"/>
-      <c r="R172" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q172" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R172" s="8" t="n"/>
       <c r="S172" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16851,7 +17780,12 @@
       </c>
       <c r="T172" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U172" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -16932,12 +17866,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q173" s="8" t="n"/>
-      <c r="R173" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q173" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R173" s="8" t="n"/>
       <c r="S173" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -16945,7 +17879,12 @@
       </c>
       <c r="T173" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U173" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17026,12 +17965,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q174" s="8" t="n"/>
-      <c r="R174" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q174" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R174" s="8" t="n"/>
       <c r="S174" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -17039,7 +17978,12 @@
       </c>
       <c r="T174" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U174" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17120,12 +18064,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q175" s="8" t="n"/>
-      <c r="R175" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q175" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R175" s="8" t="n"/>
       <c r="S175" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -17133,7 +18077,12 @@
       </c>
       <c r="T175" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U175" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17214,12 +18163,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q176" s="8" t="n"/>
-      <c r="R176" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q176" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R176" s="8" t="n"/>
       <c r="S176" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -17227,7 +18176,12 @@
       </c>
       <c r="T176" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U176" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17308,12 +18262,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q177" s="8" t="n"/>
-      <c r="R177" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q177" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R177" s="8" t="n"/>
       <c r="S177" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -17321,7 +18275,12 @@
       </c>
       <c r="T177" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U177" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17402,12 +18361,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q178" s="8" t="n"/>
-      <c r="R178" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q178" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R178" s="8" t="n"/>
       <c r="S178" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
@@ -17415,7 +18374,12 @@
       </c>
       <c r="T178" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U178" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17500,18 +18464,23 @@
           <t>DIPSTICK MEASUREMENT METHOD</t>
         </is>
       </c>
-      <c r="Q179" s="8" t="n"/>
-      <c r="R179" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q179" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R179" s="8" t="n"/>
       <c r="S179" s="8" t="inlineStr">
         <is>
           <t>AGREE</t>
         </is>
       </c>
       <c r="T179" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U179" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -17590,20 +18559,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q180" s="8" t="n"/>
-      <c r="R180" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q180" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R180" s="8" t="n"/>
       <c r="S180" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T180" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U180" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17680,20 +18654,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q181" s="8" t="n"/>
-      <c r="R181" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q181" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R181" s="8" t="n"/>
       <c r="S181" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T181" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U181" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17774,18 +18753,23 @@
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="Q182" s="8" t="n"/>
-      <c r="R182" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q182" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R182" s="8" t="n"/>
       <c r="S182" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T182" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U182" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -17870,20 +18854,25 @@
       </c>
       <c r="Q183" s="8" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R183" s="8" t="inlineStr">
+        <is>
           <t>BLOOD;SERUM;CEREBROSPINAL FLUID;FLUID;SWABBED MATERIAL;URINE</t>
         </is>
       </c>
-      <c r="R183" s="8" t="inlineStr">
+      <c r="S183" s="8" t="inlineStr">
         <is>
           <t>NOT_COMPARABLE</t>
         </is>
       </c>
-      <c r="S183" s="8" t="inlineStr">
-        <is>
-          <t>DISAGREE</t>
-        </is>
-      </c>
       <c r="T183" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U183" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -17962,20 +18951,25 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q184" s="8" t="n"/>
-      <c r="R184" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q184" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R184" s="8" t="n"/>
       <c r="S184" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T184" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U184" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -17990,7 +18984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -18009,10 +19003,11 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18098,20 +19093,25 @@
       </c>
       <c r="Q1" s="5" t="inlineStr">
         <is>
+          <t>orres_value_binding</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
           <t>spec_value_list</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>system_verdict</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>scale_verdict</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>method_verdict</t>
         </is>
@@ -18190,20 +19190,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="n"/>
-      <c r="R2" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="n"/>
       <c r="S2" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18280,20 +19285,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="n"/>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="n"/>
       <c r="S3" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18370,20 +19380,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="n"/>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="n"/>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18460,20 +19475,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="n"/>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="n"/>
       <c r="S5" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18550,20 +19570,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="n"/>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="n"/>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18644,18 +19669,23 @@
           <t>TEST STRIP</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="n"/>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -18734,20 +19764,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="n"/>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18824,20 +19859,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="n"/>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="n"/>
       <c r="S9" s="8" t="inlineStr">
         <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>LOINC_ONLY</t>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -18914,20 +19954,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="n"/>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -19012,18 +20057,23 @@
           <t>DIPSTICK MEASUREMENT METHOD</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="n"/>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -19102,20 +20152,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="n"/>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -19196,18 +20251,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="n"/>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -19286,20 +20346,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="n"/>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="n"/>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -19380,18 +20445,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="n"/>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -19470,20 +20540,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q16" s="8" t="n"/>
-      <c r="R16" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="n"/>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -19564,18 +20639,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="n"/>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -19658,18 +20738,23 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>LOINC_ONLY</t>
         </is>
@@ -19752,20 +20837,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -19846,20 +20936,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>DISAGREE</t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>AGREE</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -19936,20 +21031,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20026,20 +21126,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20116,20 +21221,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20206,20 +21316,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="n"/>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20296,20 +21411,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="n"/>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20386,20 +21506,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="n"/>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20476,20 +21601,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="n"/>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20566,20 +21696,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20656,20 +21791,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="n"/>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20746,20 +21886,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q30" s="8" t="n"/>
-      <c r="R30" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20836,20 +21981,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q31" s="8" t="n"/>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="n"/>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -20926,20 +22076,25 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="Q32" s="8" t="n"/>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
@@ -21020,18 +22175,23 @@
           <t>IMMUNOASSAY</t>
         </is>
       </c>
-      <c r="Q33" s="8" t="n"/>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="n"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -21116,20 +22276,25 @@
       </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
           <t>BLOOD;SERUM;CEREBROSPINAL FLUID;FLUID;SWABBED MATERIAL;URINE</t>
         </is>
       </c>
-      <c r="R34" s="8" t="inlineStr">
+      <c r="S34" s="8" t="inlineStr">
         <is>
           <t>NOT_COMPARABLE</t>
         </is>
       </c>
-      <c r="S34" s="8" t="inlineStr">
-        <is>
-          <t>DISAGREE</t>
-        </is>
-      </c>
       <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>BOTH_PINNED</t>
         </is>
@@ -21208,20 +22373,25 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q35" s="8" t="n"/>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t>AGREE</t>
-        </is>
-      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="n"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>DISAGREE</t>
+          <t>AGREE</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>LOINC_ONLY</t>
+          <t>PACKAGE_UNBOUND</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
         </is>
       </c>
     </row>
